--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Transaction_List_by_Vendor.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Transaction_List_by_Vendor.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="J7" s="1" t="n">
-        <v>3073.93</v>
+        <v>2878.85</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="10">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="12">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="14">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="16">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="18">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="J19" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="20">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="J21" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="22">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="J23" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="24">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="J25" s="1" t="n">
-        <v>1024.64</v>
+        <v>959.62</v>
       </c>
     </row>
     <row r="26">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="J27" s="1" t="n">
-        <v>179.31</v>
+        <v>959.5700000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="J48" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="49">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="J49" s="1" t="n">
-        <v>-722.09</v>
+        <v>-241.55</v>
       </c>
     </row>
     <row r="50">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="J50" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="51">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="J51" s="1" t="n">
-        <v>-722.09</v>
+        <v>-241.55</v>
       </c>
     </row>
     <row r="52">
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="J52" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="53">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="J53" s="1" t="n">
-        <v>-722.09</v>
+        <v>-241.55</v>
       </c>
     </row>
     <row r="54">
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="J54" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="55">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="J55" s="1" t="n">
-        <v>-722.09</v>
+        <v>-241.55</v>
       </c>
     </row>
     <row r="56">
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="J56" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="57">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="J57" s="1" t="n">
-        <v>-722.09</v>
+        <v>-241.55</v>
       </c>
     </row>
     <row r="58">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="J58" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="59">
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="J59" s="1" t="n">
-        <v>-722.09</v>
+        <v>-241.55</v>
       </c>
     </row>
     <row r="60">
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="J60" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="61">
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="J61" s="1" t="n">
-        <v>-722.09</v>
+        <v>-241.55</v>
       </c>
     </row>
     <row r="62">
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="J62" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="63">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="J63" s="1" t="n">
-        <v>-722.09</v>
+        <v>-241.55</v>
       </c>
     </row>
     <row r="64">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="J64" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="65">
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="J65" s="1" t="n">
-        <v>-722.09</v>
+        <v>-241.55</v>
       </c>
     </row>
     <row r="66">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="J66" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="67">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="J67" s="1" t="n">
-        <v>-722.09</v>
+        <v>-241.55</v>
       </c>
     </row>
     <row r="68">
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="J68" s="1" t="n">
-        <v>714</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="69">
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="J69" s="1" t="n">
-        <v>-722.1</v>
+        <v>-241.5</v>
       </c>
     </row>
     <row r="70">
@@ -3086,7 +3086,7 @@
         </is>
       </c>
       <c r="J70" s="1" t="n">
-        <v>714</v>
+        <v>169.37</v>
       </c>
     </row>
     <row r="71">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="J71" s="1" t="n">
-        <v>625</v>
+        <v>-625</v>
       </c>
     </row>
     <row r="72">
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="J120" s="1" t="n">
-        <v>4950</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="121">
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="J121" s="1" t="n">
-        <v>4975</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="122">
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="J122" s="1" t="n">
-        <v>4900</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="123">
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="J123" s="1" t="n">
-        <v>-4950</v>
+        <v>-2450</v>
       </c>
     </row>
     <row r="124">
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="J124" s="1" t="n">
-        <v>-4975</v>
+        <v>-2475</v>
       </c>
     </row>
     <row r="125">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="J125" s="1" t="n">
-        <v>-4900</v>
+        <v>-2400</v>
       </c>
     </row>
     <row r="126">
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="J180" s="1" t="n">
-        <v>-133449.16</v>
+        <v>-133425.67</v>
       </c>
     </row>
     <row r="181">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="J183" s="1" t="n">
-        <v>-133449.16</v>
+        <v>-133425.67</v>
       </c>
     </row>
     <row r="184">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="J186" s="1" t="n">
-        <v>-133449.16</v>
+        <v>-133425.67</v>
       </c>
     </row>
     <row r="187">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="J189" s="1" t="n">
-        <v>-133449.16</v>
+        <v>-133425.67</v>
       </c>
     </row>
     <row r="190">
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="J192" s="1" t="n">
-        <v>-133449.16</v>
+        <v>-133425.67</v>
       </c>
     </row>
     <row r="193">
@@ -7924,7 +7924,7 @@
         </is>
       </c>
       <c r="J195" s="1" t="n">
-        <v>-133449.16</v>
+        <v>-133425.67</v>
       </c>
     </row>
     <row r="196">
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="J198" s="1" t="n">
-        <v>-133449.16</v>
+        <v>-133425.67</v>
       </c>
     </row>
     <row r="199">
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="J201" s="1" t="n">
-        <v>-133449.16</v>
+        <v>-133425.67</v>
       </c>
     </row>
     <row r="202">
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="J204" s="1" t="n">
-        <v>-133449.16</v>
+        <v>-133425.67</v>
       </c>
     </row>
     <row r="205">
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="J207" s="1" t="n">
-        <v>-133449.16</v>
+        <v>-133425.67</v>
       </c>
     </row>
     <row r="208">
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="J210" s="1" t="n">
-        <v>-133449.16</v>
+        <v>-133425.69</v>
       </c>
     </row>
     <row r="211">
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="J216" s="1" t="n">
-        <v>1528704.04</v>
+        <v>1528962.41</v>
       </c>
     </row>
     <row r="217">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Shop equipment rental</t>
+          <t>Delivery equipment rental</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>67000 Office Supplies</t>
+          <t>66000 Freight Out</t>
         </is>
       </c>
       <c r="J289" s="1" t="n">
@@ -11600,7 +11600,7 @@
         </is>
       </c>
       <c r="J293" s="1" t="n">
-        <v>-8124.91</v>
+        <v>-7866.58</v>
       </c>
     </row>
     <row r="294">
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="J294" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="295">
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="J295" s="1" t="n">
-        <v>-8124.91</v>
+        <v>-7866.58</v>
       </c>
     </row>
     <row r="296">
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="J296" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="297">
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="J297" s="1" t="n">
-        <v>-8124.91</v>
+        <v>-7866.58</v>
       </c>
     </row>
     <row r="298">
@@ -11817,7 +11817,7 @@
         </is>
       </c>
       <c r="J298" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="299">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="J299" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="300">
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="J300" s="1" t="n">
-        <v>-8124.91</v>
+        <v>-7866.58</v>
       </c>
     </row>
     <row r="301">
@@ -11944,7 +11944,7 @@
         </is>
       </c>
       <c r="J301" s="1" t="n">
-        <v>-8124.91</v>
+        <v>-7866.58</v>
       </c>
     </row>
     <row r="302">
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="J302" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="303">
@@ -12030,7 +12030,7 @@
         </is>
       </c>
       <c r="J303" s="1" t="n">
-        <v>-8124.91</v>
+        <v>-7866.58</v>
       </c>
     </row>
     <row r="304">
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="J304" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="305">
@@ -12116,7 +12116,7 @@
         </is>
       </c>
       <c r="J305" s="1" t="n">
-        <v>-8124.91</v>
+        <v>-7866.58</v>
       </c>
     </row>
     <row r="306">
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="J306" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="307">
@@ -12202,7 +12202,7 @@
         </is>
       </c>
       <c r="J307" s="1" t="n">
-        <v>-8124.91</v>
+        <v>-7866.58</v>
       </c>
     </row>
     <row r="308">
@@ -12247,7 +12247,7 @@
         </is>
       </c>
       <c r="J308" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="309">
@@ -12288,7 +12288,7 @@
         </is>
       </c>
       <c r="J309" s="1" t="n">
-        <v>-8124.91</v>
+        <v>-7866.58</v>
       </c>
     </row>
     <row r="310">
@@ -12333,7 +12333,7 @@
         </is>
       </c>
       <c r="J310" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="311">
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="J311" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="312">
@@ -12419,7 +12419,7 @@
         </is>
       </c>
       <c r="J312" s="1" t="n">
-        <v>-8124.91</v>
+        <v>-7866.58</v>
       </c>
     </row>
     <row r="313">
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="J313" s="1" t="n">
-        <v>-8124.9</v>
+        <v>-7866.57</v>
       </c>
     </row>
     <row r="314">
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="J314" s="1" t="n">
-        <v>7989</v>
+        <v>7730.67</v>
       </c>
     </row>
     <row r="315">
@@ -12591,7 +12591,7 @@
         </is>
       </c>
       <c r="J316" s="1" t="n">
-        <v>7989</v>
+        <v>7730.63</v>
       </c>
     </row>
     <row r="317">
@@ -12642,7 +12642,7 @@
         </is>
       </c>
       <c r="J318" s="1" t="n">
-        <v>99</v>
+        <v>-159.37</v>
       </c>
     </row>
     <row r="319">
@@ -12652,7 +12652,7 @@
         </is>
       </c>
       <c r="J319" s="1" t="n">
-        <v>2881407.14</v>
+        <v>2880157.14</v>
       </c>
     </row>
     <row r="320"/>

--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Transaction_List_by_Vendor.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Transaction_List_by_Vendor.xlsx
@@ -8207,7 +8207,7 @@
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="J202" s="1" t="n">
-        <v>169202.82</v>
+        <v>18432.5</v>
       </c>
     </row>
     <row r="203">
@@ -8252,7 +8252,7 @@
         </is>
       </c>
       <c r="J203" s="1" t="n">
-        <v>169202.82</v>
+        <v>18432.5</v>
       </c>
     </row>
     <row r="204">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="J205" s="1" t="n">
-        <v>203043.39</v>
+        <v>353813.71</v>
       </c>
     </row>
     <row r="206">
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="J206" s="1" t="n">
-        <v>203043.39</v>
+        <v>353813.71</v>
       </c>
     </row>
     <row r="207">

--- a/case-studies/kestrel-valley-cycle/data/quickbooks/Transaction_List_by_Vendor.xlsx
+++ b/case-studies/kestrel-valley-cycle/data/quickbooks/Transaction_List_by_Vendor.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J323"/>
+  <dimension ref="A1:J331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7309,7 +7309,7 @@
         </is>
       </c>
       <c r="J180" s="1" t="n">
-        <v>-133425.67</v>
+        <v>-133380.79</v>
       </c>
     </row>
     <row r="181">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="J183" s="1" t="n">
-        <v>-133425.67</v>
+        <v>-133380.79</v>
       </c>
     </row>
     <row r="184">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="J186" s="1" t="n">
-        <v>-133425.67</v>
+        <v>-133380.79</v>
       </c>
     </row>
     <row r="187">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="J189" s="1" t="n">
-        <v>-133425.67</v>
+        <v>-133380.79</v>
       </c>
     </row>
     <row r="190">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="J192" s="1" t="n">
-        <v>-133425.67</v>
+        <v>-133380.79</v>
       </c>
     </row>
     <row r="193">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7924,7 +7924,7 @@
         </is>
       </c>
       <c r="J195" s="1" t="n">
-        <v>-133425.67</v>
+        <v>-133380.79</v>
       </c>
     </row>
     <row r="196">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="J198" s="1" t="n">
-        <v>-133425.67</v>
+        <v>-133380.79</v>
       </c>
     </row>
     <row r="199">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="J201" s="1" t="n">
-        <v>-133425.67</v>
+        <v>-133380.79</v>
       </c>
     </row>
     <row r="202">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="J204" s="1" t="n">
-        <v>-133425.67</v>
+        <v>-133380.79</v>
       </c>
     </row>
     <row r="205">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="J207" s="1" t="n">
-        <v>-133425.67</v>
+        <v>-133380.79</v>
       </c>
     </row>
     <row r="208">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="J210" s="1" t="n">
-        <v>-133425.69</v>
+        <v>-133380.74</v>
       </c>
     </row>
     <row r="211">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="J216" s="1" t="n">
-        <v>1528962.41</v>
+        <v>1529456.16</v>
       </c>
     </row>
     <row r="217">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -9900,29 +9900,29 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Rocky Mountain Racking</t>
+          <t>Owen Pike Hauling</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="B248" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>OPH-101</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -9932,86 +9932,159 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Warehouse racking</t>
+          <t>Freight hauling</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>15000 Furniture and Equipment</t>
+          <t>66000 Freight Out</t>
         </is>
       </c>
       <c r="J248" s="1" t="n">
-        <v>-14500</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Total for Rocky Mountain Racking</t>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>09/23/2025</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Bill Payment (Check)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J249" s="1" t="n">
-        <v>-14500</v>
+        <v>-1850</v>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Summit Tire Import</t>
-        </is>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>01/13/2026</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>OPH-102</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Freight hauling</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>66000 Freight Out</t>
+        </is>
+      </c>
+      <c r="J250" s="1" t="n">
+        <v>2100</v>
       </c>
     </row>
     <row r="251">
       <c r="B251" t="inlineStr">
         <is>
-          <t>06/21/2025</t>
+          <t>01/27/2026</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr"/>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
       <c r="J251" s="1" t="n">
-        <v>71065.19</v>
+        <v>-2100</v>
       </c>
     </row>
     <row r="252">
       <c r="B252" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -10021,7 +10094,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>ST-25013</t>
+          <t>OPH-103</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -10031,7 +10104,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>PO 1013</t>
+          <t>Freight hauling</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -10041,22 +10114,22 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>12100 Inventory Asset</t>
+          <t>66000 Freight Out</t>
         </is>
       </c>
       <c r="J252" s="1" t="n">
-        <v>71065.19</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="253">
       <c r="B253" t="inlineStr">
         <is>
-          <t>07/18/2025</t>
+          <t>04/28/2026</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -10066,7 +10139,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -10086,95 +10159,30 @@
         </is>
       </c>
       <c r="J253" s="1" t="n">
-        <v>-79747.81</v>
+        <v>-1975</v>
       </c>
     </row>
     <row r="254">
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>07/23/2025</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Purchase Order</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr"/>
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Total for Owen Pike Hauling</t>
+        </is>
+      </c>
       <c r="J254" s="1" t="n">
-        <v>71065.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>08/04/2025</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>ST-25014</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>PO 1014</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>12100 Inventory Asset</t>
-        </is>
-      </c>
-      <c r="J255" s="1" t="n">
-        <v>71065.19</v>
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Rocky Mountain Racking</t>
+        </is>
       </c>
     </row>
     <row r="256">
       <c r="B256" t="inlineStr">
         <is>
-          <t>08/18/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -10184,12 +10192,12 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -10197,7 +10205,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Warehouse racking</t>
+        </is>
+      </c>
       <c r="H256" t="inlineStr">
         <is>
           <t>10100 Checking - First Prairie</t>
@@ -10205,99 +10217,34 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>15000 Furniture and Equipment</t>
         </is>
       </c>
       <c r="J256" s="1" t="n">
-        <v>-79747.81</v>
+        <v>-14500</v>
       </c>
     </row>
     <row r="257">
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>08/24/2025</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Purchase Order</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr"/>
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Total for Rocky Mountain Racking</t>
+        </is>
+      </c>
       <c r="J257" s="1" t="n">
-        <v>60913.02</v>
+        <v>-14500</v>
       </c>
     </row>
     <row r="258">
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>09/05/2025</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>ST-25015</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>PO 1015</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>12100 Inventory Asset</t>
-        </is>
-      </c>
-      <c r="J258" s="1" t="n">
-        <v>60913.02</v>
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Summit Tire Import</t>
+        </is>
       </c>
     </row>
     <row r="259">
       <c r="B259" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>06/21/2025</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -10307,38 +10254,34 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
       <c r="J259" s="1" t="n">
-        <v>-79747.81</v>
+        <v>71065.19</v>
       </c>
     </row>
     <row r="260">
       <c r="B260" t="inlineStr">
         <is>
-          <t>09/24/2025</t>
+          <t>07/03/2025</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -10348,34 +10291,42 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>ST-25013</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>PO 1013</t>
+        </is>
+      </c>
       <c r="H260" t="inlineStr">
         <is>
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>12100 Inventory Asset</t>
+        </is>
+      </c>
       <c r="J260" s="1" t="n">
-        <v>50760.85</v>
+        <v>71065.19</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>07/18/2025</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -10385,12 +10336,12 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>ST-25016</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -10398,29 +10349,25 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>PO 1016</t>
-        </is>
-      </c>
+      <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>12100 Inventory Asset</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J261" s="1" t="n">
-        <v>50760.85</v>
+        <v>-79747.81</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>07/23/2025</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -10430,38 +10377,34 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
       <c r="J262" s="1" t="n">
-        <v>-79747.81</v>
+        <v>71065.19</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" t="inlineStr">
         <is>
-          <t>10/26/2025</t>
+          <t>08/04/2025</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -10471,34 +10414,42 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>ST-25014</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>PO 1014</t>
+        </is>
+      </c>
       <c r="H263" t="inlineStr">
         <is>
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>12100 Inventory Asset</t>
+        </is>
+      </c>
       <c r="J263" s="1" t="n">
-        <v>40608.68</v>
+        <v>71065.19</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" t="inlineStr">
         <is>
-          <t>11/07/2025</t>
+          <t>08/18/2025</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -10508,12 +10459,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>ST-25017</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -10521,29 +10472,25 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>PO 1017</t>
-        </is>
-      </c>
+      <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>12100 Inventory Asset</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J264" s="1" t="n">
-        <v>40608.68</v>
+        <v>-79747.81</v>
       </c>
     </row>
     <row r="265">
       <c r="B265" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>08/24/2025</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -10553,38 +10500,34 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
       <c r="J265" s="1" t="n">
-        <v>-79747.81</v>
+        <v>60913.02</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" t="inlineStr">
         <is>
-          <t>11/21/2025</t>
+          <t>09/05/2025</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -10594,34 +10537,42 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>ST-25015</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>PO 1015</t>
+        </is>
+      </c>
       <c r="H266" t="inlineStr">
         <is>
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>12100 Inventory Asset</t>
+        </is>
+      </c>
       <c r="J266" s="1" t="n">
-        <v>50760.85</v>
+        <v>60913.02</v>
       </c>
     </row>
     <row r="267">
       <c r="B267" t="inlineStr">
         <is>
-          <t>12/03/2025</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -10631,12 +10582,12 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>ST-25018</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -10644,29 +10595,25 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>PO 1018</t>
-        </is>
-      </c>
+      <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>12100 Inventory Asset</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J267" s="1" t="n">
-        <v>50760.85</v>
+        <v>-79747.81</v>
       </c>
     </row>
     <row r="268">
       <c r="B268" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>09/24/2025</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -10676,38 +10623,34 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
       <c r="J268" s="1" t="n">
-        <v>-79747.81</v>
+        <v>50760.85</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" t="inlineStr">
         <is>
-          <t>12/24/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -10717,34 +10660,42 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>ST-25016</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>PO 1016</t>
+        </is>
+      </c>
       <c r="H269" t="inlineStr">
         <is>
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>12100 Inventory Asset</t>
+        </is>
+      </c>
       <c r="J269" s="1" t="n">
-        <v>60913.02</v>
+        <v>50760.85</v>
       </c>
     </row>
     <row r="270">
       <c r="B270" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -10754,12 +10705,12 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>ST-25019</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -10767,29 +10718,25 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>PO 1019</t>
-        </is>
-      </c>
+      <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>12100 Inventory Asset</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J270" s="1" t="n">
-        <v>60913.02</v>
+        <v>-79747.81</v>
       </c>
     </row>
     <row r="271">
       <c r="B271" t="inlineStr">
         <is>
-          <t>01/19/2026</t>
+          <t>10/26/2025</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -10799,38 +10746,34 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
       <c r="J271" s="1" t="n">
-        <v>-79747.81</v>
+        <v>40608.68</v>
       </c>
     </row>
     <row r="272">
       <c r="B272" t="inlineStr">
         <is>
-          <t>01/24/2026</t>
+          <t>11/07/2025</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -10840,34 +10783,42 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>ST-25017</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>PO 1017</t>
+        </is>
+      </c>
       <c r="H272" t="inlineStr">
         <is>
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>12100 Inventory Asset</t>
+        </is>
+      </c>
       <c r="J272" s="1" t="n">
-        <v>81217.35000000001</v>
+        <v>40608.68</v>
       </c>
     </row>
     <row r="273">
       <c r="B273" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -10877,12 +10828,12 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>ST-25020</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -10890,29 +10841,25 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>PO 1020</t>
-        </is>
-      </c>
+      <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>12100 Inventory Asset</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J273" s="1" t="n">
-        <v>81217.35000000001</v>
+        <v>-79747.81</v>
       </c>
     </row>
     <row r="274">
       <c r="B274" t="inlineStr">
         <is>
-          <t>02/18/2026</t>
+          <t>11/21/2025</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -10922,38 +10869,34 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
       <c r="J274" s="1" t="n">
-        <v>-79747.81</v>
+        <v>50760.85</v>
       </c>
     </row>
     <row r="275">
       <c r="B275" t="inlineStr">
         <is>
-          <t>02/22/2026</t>
+          <t>12/03/2025</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -10963,34 +10906,42 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>ST-25018</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G275" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>PO 1018</t>
+        </is>
+      </c>
       <c r="H275" t="inlineStr">
         <is>
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>12100 Inventory Asset</t>
+        </is>
+      </c>
       <c r="J275" s="1" t="n">
-        <v>90644.37</v>
+        <v>50760.85</v>
       </c>
     </row>
     <row r="276">
       <c r="B276" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -11000,12 +10951,12 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>ST-25021</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -11013,29 +10964,25 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>PO 1021</t>
-        </is>
-      </c>
+      <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>12100 Inventory Asset</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J276" s="1" t="n">
-        <v>101521.69</v>
+        <v>-79747.81</v>
       </c>
     </row>
     <row r="277">
       <c r="B277" t="inlineStr">
         <is>
-          <t>03/18/2026</t>
+          <t>12/24/2025</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -11045,38 +10992,34 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr"/>
       <c r="J277" s="1" t="n">
-        <v>-79747.81</v>
+        <v>60913.02</v>
       </c>
     </row>
     <row r="278">
       <c r="B278" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -11086,34 +11029,42 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>ST-25019</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>PO 1019</t>
+        </is>
+      </c>
       <c r="H278" t="inlineStr">
         <is>
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>12100 Inventory Asset</t>
+        </is>
+      </c>
       <c r="J278" s="1" t="n">
-        <v>121826.03</v>
+        <v>60913.02</v>
       </c>
     </row>
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>01/19/2026</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -11123,12 +11074,12 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>ST-25022</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -11136,29 +11087,25 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>PO 1022</t>
-        </is>
-      </c>
+      <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>12100 Inventory Asset</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J279" s="1" t="n">
-        <v>121826.03</v>
+        <v>-79747.81</v>
       </c>
     </row>
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t>04/20/2026</t>
+          <t>01/24/2026</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -11168,38 +11115,34 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
       <c r="J280" s="1" t="n">
-        <v>-79747.81</v>
+        <v>81217.35000000001</v>
       </c>
     </row>
     <row r="281">
       <c r="B281" t="inlineStr">
         <is>
-          <t>04/22/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -11209,34 +11152,42 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>ST-25020</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>PO 1020</t>
+        </is>
+      </c>
       <c r="H281" t="inlineStr">
         <is>
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>12100 Inventory Asset</t>
+        </is>
+      </c>
       <c r="J281" s="1" t="n">
-        <v>111673.86</v>
+        <v>81217.35000000001</v>
       </c>
     </row>
     <row r="282">
       <c r="B282" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>02/18/2026</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -11246,12 +11197,12 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>ST-25023</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -11259,29 +11210,25 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>PO 1023</t>
-        </is>
-      </c>
+      <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>12100 Inventory Asset</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J282" s="1" t="n">
-        <v>111673.86</v>
+        <v>-79747.81</v>
       </c>
     </row>
     <row r="283">
       <c r="B283" t="inlineStr">
         <is>
-          <t>05/18/2026</t>
+          <t>02/22/2026</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -11291,38 +11238,34 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
       <c r="J283" s="1" t="n">
-        <v>-79747.78999999999</v>
+        <v>90644.37</v>
       </c>
     </row>
     <row r="284">
       <c r="B284" t="inlineStr">
         <is>
-          <t>05/23/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -11332,34 +11275,42 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Purchase Order</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>ST-25021</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>PO 1021</t>
+        </is>
+      </c>
       <c r="H284" t="inlineStr">
         <is>
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>12100 Inventory Asset</t>
+        </is>
+      </c>
       <c r="J284" s="1" t="n">
-        <v>91369.50999999999</v>
+        <v>101521.69</v>
       </c>
     </row>
     <row r="285">
       <c r="B285" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>03/18/2026</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -11369,12 +11320,12 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>ST-25024</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -11382,29 +11333,25 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>PO 1024</t>
-        </is>
-      </c>
+      <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>12100 Inventory Asset</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J285" s="1" t="n">
-        <v>91369.50999999999</v>
+        <v>-79747.81</v>
       </c>
     </row>
     <row r="286">
       <c r="B286" t="inlineStr">
         <is>
-          <t>06/16/2026</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -11414,55 +11361,120 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr"/>
       <c r="J286" s="1" t="n">
-        <v>-17480.25</v>
+        <v>121826.03</v>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>Total for Summit Tire Import</t>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>ST-25022</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>PO 1022</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>12100 Inventory Asset</t>
         </is>
       </c>
       <c r="J287" s="1" t="n">
-        <v>921807.02</v>
+        <v>121826.03</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Tri-County Tool Rental</t>
-        </is>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Bill Payment (Check)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="J288" s="1" t="n">
+        <v>-79747.81</v>
       </c>
     </row>
     <row r="289">
       <c r="B289" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>04/22/2026</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -11472,42 +11484,34 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Purchase Order</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>TC-8812</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>Delivery equipment rental</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr">
         <is>
           <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>66000 Freight Out</t>
-        </is>
-      </c>
+      <c r="I289" t="inlineStr"/>
       <c r="J289" s="1" t="n">
-        <v>3100</v>
+        <v>111673.86</v>
       </c>
     </row>
     <row r="290">
       <c r="B290" t="inlineStr">
         <is>
-          <t>06/27/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -11517,55 +11521,120 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>ST-25023</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>PO 1023</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>12100 Inventory Asset</t>
+        </is>
+      </c>
+      <c r="J290" s="1" t="n">
+        <v>111673.86</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
           <t>Bill Payment (Check)</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>4421</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
-      <c r="J290" s="1" t="n">
-        <v>-3100</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>Total for Tri-County Tool Rental</t>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>4407</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J291" s="1" t="n">
-        <v>0</v>
+        <v>-79747.78999999999</v>
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>Velo Freight Lines</t>
-        </is>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>05/23/2026</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Purchase Order</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" s="1" t="n">
+        <v>91369.50999999999</v>
       </c>
     </row>
     <row r="293">
       <c r="B293" t="inlineStr">
         <is>
-          <t>07/18/2025</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -11575,12 +11644,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>ST-25024</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -11588,25 +11657,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>PO 1024</t>
+        </is>
+      </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>12100 Inventory Asset</t>
         </is>
       </c>
       <c r="J293" s="1" t="n">
-        <v>-7866.58</v>
+        <v>91369.50999999999</v>
       </c>
     </row>
     <row r="294">
       <c r="B294" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>06/16/2026</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -11616,12 +11689,12 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>VF-001</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -11629,115 +11702,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>Freight out</t>
-        </is>
-      </c>
+      <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>66000 Freight Out</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J294" s="1" t="n">
-        <v>7730.67</v>
+        <v>-17480.25</v>
       </c>
     </row>
     <row r="295">
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>08/18/2025</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>Bill Payment (Check)</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>4023</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr"/>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Total for Summit Tire Import</t>
         </is>
       </c>
       <c r="J295" s="1" t="n">
-        <v>-7866.58</v>
+        <v>921807.02</v>
       </c>
     </row>
     <row r="296">
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>08/20/2025</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>VF-002</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>Freight out</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t>66000 Freight Out</t>
-        </is>
-      </c>
-      <c r="J296" s="1" t="n">
-        <v>7730.67</v>
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Tri-County Tool Rental</t>
+        </is>
       </c>
     </row>
     <row r="297">
       <c r="B297" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -11747,12 +11747,12 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>TC-8812</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -11760,25 +11760,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Delivery equipment rental</t>
+        </is>
+      </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>66000 Freight Out</t>
         </is>
       </c>
       <c r="J297" s="1" t="n">
-        <v>-7866.58</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="298">
       <c r="B298" t="inlineStr">
         <is>
-          <t>09/22/2025</t>
+          <t>06/27/2026</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -11788,12 +11792,12 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>VF-003</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -11801,115 +11805,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>Freight out</t>
-        </is>
-      </c>
+      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>66000 Freight Out</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J298" s="1" t="n">
-        <v>7730.67</v>
+        <v>-3100</v>
       </c>
     </row>
     <row r="299">
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>10/20/2025</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>VF-004</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>Freight out</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>66000 Freight Out</t>
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Total for Tri-County Tool Rental</t>
         </is>
       </c>
       <c r="J299" s="1" t="n">
-        <v>7730.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>10/20/2025</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Bill Payment (Check)</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>4049</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>10100 Checking - First Prairie</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>20000 Accounts Payable (A/P)</t>
-        </is>
-      </c>
-      <c r="J300" s="1" t="n">
-        <v>-7866.58</v>
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Velo Freight Lines</t>
+        </is>
       </c>
     </row>
     <row r="301">
       <c r="B301" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>07/18/2025</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -11924,7 +11855,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -11944,13 +11875,13 @@
         </is>
       </c>
       <c r="J301" s="1" t="n">
-        <v>-7866.58</v>
+        <v>-7372.83</v>
       </c>
     </row>
     <row r="302">
       <c r="B302" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -11965,7 +11896,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>VF-005</t>
+          <t>VF-001</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -11989,13 +11920,13 @@
         </is>
       </c>
       <c r="J302" s="1" t="n">
-        <v>7730.67</v>
+        <v>7236.92</v>
       </c>
     </row>
     <row r="303">
       <c r="B303" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>08/18/2025</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -12010,7 +11941,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -12030,13 +11961,13 @@
         </is>
       </c>
       <c r="J303" s="1" t="n">
-        <v>-7866.58</v>
+        <v>-7372.83</v>
       </c>
     </row>
     <row r="304">
       <c r="B304" t="inlineStr">
         <is>
-          <t>12/22/2025</t>
+          <t>08/20/2025</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -12051,7 +11982,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>VF-006</t>
+          <t>VF-002</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -12075,13 +12006,13 @@
         </is>
       </c>
       <c r="J304" s="1" t="n">
-        <v>7730.67</v>
+        <v>7236.92</v>
       </c>
     </row>
     <row r="305">
       <c r="B305" t="inlineStr">
         <is>
-          <t>01/19/2026</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -12096,7 +12027,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -12116,13 +12047,13 @@
         </is>
       </c>
       <c r="J305" s="1" t="n">
-        <v>-7866.58</v>
+        <v>-7372.83</v>
       </c>
     </row>
     <row r="306">
       <c r="B306" t="inlineStr">
         <is>
-          <t>01/20/2026</t>
+          <t>09/22/2025</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -12137,7 +12068,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>VF-007</t>
+          <t>VF-003</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -12161,13 +12092,13 @@
         </is>
       </c>
       <c r="J306" s="1" t="n">
-        <v>7730.67</v>
+        <v>7236.92</v>
       </c>
     </row>
     <row r="307">
       <c r="B307" t="inlineStr">
         <is>
-          <t>02/18/2026</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -12177,12 +12108,12 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>VF-004</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -12190,25 +12121,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Freight out</t>
+        </is>
+      </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>66000 Freight Out</t>
         </is>
       </c>
       <c r="J307" s="1" t="n">
-        <v>-7866.58</v>
+        <v>7236.92</v>
       </c>
     </row>
     <row r="308">
       <c r="B308" t="inlineStr">
         <is>
-          <t>02/20/2026</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -12218,12 +12153,12 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>VF-008</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -12231,29 +12166,25 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>Freight out</t>
-        </is>
-      </c>
+      <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>66000 Freight Out</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J308" s="1" t="n">
-        <v>7730.67</v>
+        <v>-7372.83</v>
       </c>
     </row>
     <row r="309">
       <c r="B309" t="inlineStr">
         <is>
-          <t>03/18/2026</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -12268,7 +12199,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -12288,13 +12219,13 @@
         </is>
       </c>
       <c r="J309" s="1" t="n">
-        <v>-7866.58</v>
+        <v>-7372.83</v>
       </c>
     </row>
     <row r="310">
       <c r="B310" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -12309,7 +12240,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>VF-009</t>
+          <t>VF-005</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -12333,13 +12264,13 @@
         </is>
       </c>
       <c r="J310" s="1" t="n">
-        <v>7730.67</v>
+        <v>7236.92</v>
       </c>
     </row>
     <row r="311">
       <c r="B311" t="inlineStr">
         <is>
-          <t>04/20/2026</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -12349,12 +12280,12 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Bill Payment (Check)</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>VF-010</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -12362,29 +12293,25 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>Freight out</t>
-        </is>
-      </c>
+      <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>10100 Checking - First Prairie</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>66000 Freight Out</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="J311" s="1" t="n">
-        <v>7730.67</v>
+        <v>-7372.83</v>
       </c>
     </row>
     <row r="312">
       <c r="B312" t="inlineStr">
         <is>
-          <t>04/20/2026</t>
+          <t>12/22/2025</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -12394,12 +12321,12 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Bill Payment (Check)</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>VF-006</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -12407,25 +12334,29 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Freight out</t>
+        </is>
+      </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>10100 Checking - First Prairie</t>
+          <t>20000 Accounts Payable (A/P)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>20000 Accounts Payable (A/P)</t>
+          <t>66000 Freight Out</t>
         </is>
       </c>
       <c r="J312" s="1" t="n">
-        <v>-7866.58</v>
+        <v>7236.92</v>
       </c>
     </row>
     <row r="313">
       <c r="B313" t="inlineStr">
         <is>
-          <t>05/18/2026</t>
+          <t>01/19/2026</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -12440,7 +12371,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -12460,13 +12391,13 @@
         </is>
       </c>
       <c r="J313" s="1" t="n">
-        <v>-7866.57</v>
+        <v>-7372.83</v>
       </c>
     </row>
     <row r="314">
       <c r="B314" t="inlineStr">
         <is>
-          <t>05/20/2026</t>
+          <t>01/20/2026</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -12481,7 +12412,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>VF-011</t>
+          <t>VF-007</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -12505,13 +12436,13 @@
         </is>
       </c>
       <c r="J314" s="1" t="n">
-        <v>7730.67</v>
+        <v>7236.92</v>
       </c>
     </row>
     <row r="315">
       <c r="B315" t="inlineStr">
         <is>
-          <t>06/11/2026</t>
+          <t>02/18/2026</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -12526,7 +12457,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -12546,13 +12477,13 @@
         </is>
       </c>
       <c r="J315" s="1" t="n">
-        <v>-3915</v>
+        <v>-7372.83</v>
       </c>
     </row>
     <row r="316">
       <c r="B316" t="inlineStr">
         <is>
-          <t>06/22/2026</t>
+          <t>02/20/2026</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -12567,7 +12498,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>VF-012</t>
+          <t>VF-008</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -12591,13 +12522,13 @@
         </is>
       </c>
       <c r="J316" s="1" t="n">
-        <v>7730.63</v>
+        <v>7236.92</v>
       </c>
     </row>
     <row r="317">
       <c r="B317" t="inlineStr">
         <is>
-          <t>06/22/2026</t>
+          <t>03/18/2026</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -12612,7 +12543,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -12632,34 +12563,378 @@
         </is>
       </c>
       <c r="J317" s="1" t="n">
+        <v>-7372.83</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>03/20/2026</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>VF-009</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Freight out</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>66000 Freight Out</t>
+        </is>
+      </c>
+      <c r="J318" s="1" t="n">
+        <v>7236.92</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>VF-010</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Freight out</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>66000 Freight Out</t>
+        </is>
+      </c>
+      <c r="J319" s="1" t="n">
+        <v>7236.92</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>04/20/2026</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Bill Payment (Check)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>4395</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="J320" s="1" t="n">
+        <v>-7372.83</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>05/18/2026</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Bill Payment (Check)</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>4408</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="J321" s="1" t="n">
+        <v>-7372.82</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>05/20/2026</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>VF-011</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Freight out</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>66000 Freight Out</t>
+        </is>
+      </c>
+      <c r="J322" s="1" t="n">
+        <v>7236.92</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Bill Payment (Check)</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="J323" s="1" t="n">
+        <v>-3915</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>06/22/2026</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>VF-012</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Freight out</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>66000 Freight Out</t>
+        </is>
+      </c>
+      <c r="J324" s="1" t="n">
+        <v>7236.88</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>06/22/2026</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Bill Payment (Check)</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>4418</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>10100 Checking - First Prairie</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>20000 Accounts Payable (A/P)</t>
+        </is>
+      </c>
+      <c r="J325" s="1" t="n">
         <v>-2480</v>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
+    <row r="326">
+      <c r="A326" t="inlineStr">
         <is>
           <t>Total for Velo Freight Lines</t>
         </is>
       </c>
-      <c r="J318" s="1" t="n">
-        <v>-159.37</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
+      <c r="J326" s="1" t="n">
+        <v>-653.12</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="J319" s="1" t="n">
+      <c r="J327" s="1" t="n">
         <v>2880157.14</v>
       </c>
     </row>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323">
-      <c r="A323" t="inlineStr">
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331">
+      <c r="A331" t="inlineStr">
         <is>
           <t xml:space="preserve"> Wednesday, July 15, 2026 10:50 AM GMTZ</t>
         </is>
